--- a/Result/profitability/1783.xlsx
+++ b/Result/profitability/1783.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.6525</v>
       </c>
       <c r="N2" t="n">
-        <v>67.55125000000001</v>
+        <v>66.84</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.55625</v>
+        <v>0.5925</v>
       </c>
       <c r="N3" t="n">
-        <v>63.635</v>
+        <v>62.97125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.475</v>
+        <v>0.51875</v>
       </c>
       <c r="N4" t="n">
-        <v>59.84625</v>
+        <v>59.52625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.37625</v>
+        <v>0.40375</v>
       </c>
       <c r="N5" t="n">
-        <v>55.09500000000001</v>
+        <v>55.33875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8431,6 +8431,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>221</v>
+      </c>
+      <c r="D64" t="n">
+        <v>70</v>
+      </c>
+      <c r="E64" t="n">
+        <v>151</v>
+      </c>
+      <c r="F64" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="G64" t="n">
+        <v>57</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>25.69%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>8</v>
+      </c>
+      <c r="J64" t="n">
+        <v>64</v>
+      </c>
+      <c r="K64" t="n">
+        <v>79</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="N64" t="n">
+        <v>70.43625</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-2.379999999999995</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.03375886524822691</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.950000000000003</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.02946954813359537</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
